--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486390_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486390_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7331</v>
+        <v>6.1754</v>
       </c>
       <c r="E2" t="n">
-        <v>1.705</v>
+        <v>2.3323</v>
       </c>
       <c r="F2" t="n">
-        <v>4.028</v>
+        <v>3.8431</v>
       </c>
       <c r="G2" t="n">
         <v>6.0904</v>
@@ -610,13 +610,13 @@
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3889</v>
+        <v>0.0535</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4264</v>
+        <v>-0.7991</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0375</v>
+        <v>0.8526</v>
       </c>
       <c r="V2" t="n">
         <v>-1.056</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7122</v>
+        <v>4.5428</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5081</v>
+        <v>3.9552</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2041</v>
+        <v>0.5876</v>
       </c>
       <c r="G3" t="n">
         <v>4.4189</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4434</v>
+        <v>0.274</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9469</v>
+        <v>-0.4999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3903</v>
+        <v>0.7739</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8902</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4883</v>
+        <v>4.3034</v>
       </c>
       <c r="E4" t="n">
         <v>2.8315</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6569</v>
+        <v>1.4719</v>
       </c>
       <c r="G4" t="n">
         <v>4.2621</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5737</v>
+        <v>0.3887</v>
       </c>
       <c r="T4" t="n">
         <v>0.2656</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3081</v>
+        <v>0.1232</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7374</v>
+        <v>2.8364</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7907</v>
+        <v>-0.7413</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9467</v>
+        <v>3.5777</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1669</v>
+        <v>1.7241</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2585</v>
+        <v>-0.5868</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9084</v>
+        <v>2.3109</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1296</v>
+        <v>1.3202</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2857</v>
+        <v>-0.8815</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4152</v>
+        <v>2.2018</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0373</v>
+        <v>0.4038</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5442</v>
+        <v>0.2947</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5068</v>
+        <v>0.1091</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>3.6976</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2655</v>
+        <v>-0.5266</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3389</v>
+        <v>-0.4939</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6042999999999999</v>
+        <v>-0.0328</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2039</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.491</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7651</v>
+        <v>2.5516</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4119</v>
+        <v>0.6357</v>
       </c>
       <c r="F6" t="n">
-        <v>3.177</v>
+        <v>1.9159</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7241</v>
+        <v>1.1669</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5868</v>
+        <v>0.2585</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3109</v>
+        <v>0.9084</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3202</v>
+        <v>1.1296</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8815</v>
+        <v>-0.2857</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2018</v>
+        <v>1.4152</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4038</v>
+        <v>0.0373</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2947</v>
+        <v>0.5442</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1091</v>
+        <v>-0.5068</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6976</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5979</v>
+        <v>0.0796</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1644</v>
+        <v>-0.4939</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4335</v>
+        <v>0.5735</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2039</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3765</v>
+        <v>1.233</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.6425</v>
+        <v>-3.9092</v>
       </c>
       <c r="F7" t="n">
-        <v>5.019</v>
+        <v>5.1423</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2083</v>
@@ -1000,13 +1000,13 @@
         <v>3.2626</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3358</v>
+        <v>0.1923</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2692</v>
+        <v>0.0024</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1899</v>
       </c>
       <c r="V7" t="n">
         <v>0.074</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GONZALEZ LONGARELA</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0346</v>
+        <v>0.468</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5157</v>
+        <v>-2.0825</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4811</v>
+        <v>2.5505</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1093</v>
+        <v>2.1632</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1977</v>
+        <v>1.1527</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0885</v>
+        <v>1.0104</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7212</v>
+        <v>2.1098</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0182</v>
+        <v>0.0611</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7029</v>
+        <v>2.0488</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8304</v>
+        <v>0.0533</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.216</v>
+        <v>1.0916</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6144</v>
+        <v>-1.0383</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.4377</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2175</v>
+        <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0737</v>
+        <v>0.146</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2055</v>
+        <v>0.1154</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1318</v>
+        <v>0.0306</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2039</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>P. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0603</v>
+        <v>-0.0579</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.219</v>
+        <v>1.5157</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1586</v>
+        <v>-1.5736</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3448</v>
+        <v>-0.1093</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8643</v>
+        <v>-0.1977</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5195</v>
+        <v>0.0885</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0355</v>
+        <v>1.7212</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5964</v>
+        <v>0.0182</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4391</v>
+        <v>1.7029</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6907</v>
+        <v>-1.8304</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2679</v>
+        <v>-0.216</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9586</v>
+        <v>-1.6144</v>
       </c>
       <c r="P9" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2534</v>
+        <v>-0.1661</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2618</v>
+        <v>0.0394</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8135</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.198</v>
+        <v>-0.2029</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2946</v>
+        <v>-4.3307</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09669999999999999</v>
+        <v>4.1278</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.206</v>
+        <v>-1.3448</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7693</v>
+        <v>-1.8643</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4367</v>
+        <v>0.5195</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6943</v>
+        <v>-2.0355</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9765</v>
+        <v>-1.5964</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2822</v>
+        <v>-0.4391</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5117</v>
+        <v>0.6907</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2072</v>
+        <v>-0.2679</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7188</v>
+        <v>0.9586</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1751</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4627</v>
+        <v>0.1109</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1392</v>
+        <v>-0.1202</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3235</v>
+        <v>0.231</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6297</v>
+        <v>0.8135</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8902</v>
+        <v>0.8135</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2671</v>
+        <v>-1.1854</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2627</v>
+        <v>-1.3437</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9956</v>
+        <v>0.1583</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1632</v>
+        <v>-1.206</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1527</v>
+        <v>-0.7693</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0104</v>
+        <v>-0.4367</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1098</v>
+        <v>-0.6943</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0611</v>
+        <v>-1.9765</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0488</v>
+        <v>1.2822</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0533</v>
+        <v>-0.5117</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0916</v>
+        <v>1.2072</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0383</v>
+        <v>-1.7188</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0451</v>
+        <v>2.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.4377</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5891</v>
+        <v>0.4753</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0649</v>
+        <v>0.0901</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5242</v>
+        <v>0.3851</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2039</v>
+        <v>-2.6297</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X11" t="n">
-        <v>0.074</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>20.3218</v>
+        <v>20.6644</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.479700000000001</v>
+        <v>-1.136999999999999</v>
       </c>
       <c r="F12" t="n">
         <v>21.8015</v>
@@ -1372,13 +1372,13 @@
         <v>14.2084</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7277999999999999</v>
+        <v>0.7278</v>
       </c>
       <c r="N12" t="n">
         <v>3.7839</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.056</v>
+        <v>-3.056000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>6.5252</v>
@@ -1390,13 +1390,13 @@
         <v>22.8382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6848999999999996</v>
+        <v>1.0276</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4814</v>
+        <v>-2.139</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1662</v>
+        <v>3.1664</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8456</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7309</v>
+        <v>1.5543</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3495</v>
+        <v>1.6848</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6186</v>
+        <v>-0.1305</v>
       </c>
       <c r="G13" t="n">
         <v>4.98</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9865</v>
+        <v>-0.1631</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7294</v>
+        <v>-0.3941</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2571</v>
+        <v>0.231</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7438</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1322</v>
+        <v>0.005</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.876</v>
+        <v>-0.6234</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8931</v>
+        <v>-1.2457</v>
       </c>
       <c r="H14" t="n">
-        <v>1.174</v>
+        <v>-0.3923</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.0671</v>
+        <v>-0.8534</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4061</v>
+        <v>0.0867</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1383</v>
+        <v>-0.1428</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2677</v>
+        <v>0.2295</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2992</v>
+        <v>-1.3324</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9643</v>
+        <v>-0.2495</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3348</v>
+        <v>-1.0829</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2814</v>
+        <v>-0.0252</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2508</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0306</v>
+        <v>0.0565</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8535</v>
+        <v>-0.881</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1068</v>
+        <v>-0.877</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7467</v>
+        <v>-0.004</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2457</v>
+        <v>-1.7892</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3923</v>
+        <v>0.5321</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8534</v>
+        <v>-2.3212</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0867</v>
+        <v>-0.6703</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1428</v>
+        <v>0.0365</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2295</v>
+        <v>-0.7068</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3324</v>
+        <v>-1.1188</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2495</v>
+        <v>0.4956</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0829</v>
+        <v>-1.6144</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2603</v>
+        <v>-0.3969</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1935</v>
+        <v>-0.2067</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0668</v>
+        <v>-0.1902</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2959</v>
+        <v>-1.5584</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9887</v>
+        <v>-1.9901</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3071</v>
+        <v>0.4318</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7892</v>
+        <v>-1.4778</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5321</v>
+        <v>0.2553</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3212</v>
+        <v>-1.7332</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6703</v>
+        <v>-0.3342</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0365</v>
+        <v>-0.1063</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7068</v>
+        <v>-0.2279</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1188</v>
+        <v>-1.1436</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4956</v>
+        <v>0.3617</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6144</v>
+        <v>-1.5053</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8117</v>
+        <v>-0.0805</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3184</v>
+        <v>-0.5684</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4933</v>
+        <v>0.4879</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0142</v>
+        <v>-1.6636</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9688</v>
+        <v>-3.0805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9546</v>
+        <v>1.417</v>
       </c>
       <c r="G17" t="n">
         <v>-2.0672</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4897</v>
+        <v>-0.1391</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6128</v>
+        <v>-0.7246</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1232</v>
+        <v>0.5855</v>
       </c>
       <c r="V17" t="n">
         <v>0.7602</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0311</v>
+        <v>-2.1214</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4372</v>
+        <v>-0.4855</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4061</v>
+        <v>-1.636</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4778</v>
+        <v>-3.7699</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2553</v>
+        <v>-2.4878</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7332</v>
+        <v>-1.2822</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3342</v>
+        <v>-1.4007</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1063</v>
+        <v>-2.0709</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2279</v>
+        <v>0.6702</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1436</v>
+        <v>-2.3692</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3617</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5053</v>
+        <v>-1.9523</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5533</v>
+        <v>-0.3515</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0154</v>
+        <v>-0.2572</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4622</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6417</v>
+        <v>-2.686</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8208</v>
+        <v>-1.6559</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8209</v>
+        <v>-1.0301</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7699</v>
+        <v>-0.8931</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4878</v>
+        <v>1.174</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2822</v>
+        <v>-2.0671</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4007</v>
+        <v>2.4061</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0709</v>
+        <v>2.1383</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6702</v>
+        <v>0.2677</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3692</v>
+        <v>-3.2992</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4169</v>
+        <v>-0.9643</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9523</v>
+        <v>-2.3348</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8717</v>
+        <v>0.3392</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5924</v>
+        <v>0.4627</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2793</v>
+        <v>-0.1235</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>-0.1745</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>-0.1745</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0893</v>
+        <v>-3.3667</v>
       </c>
       <c r="E20" t="n">
         <v>-5.2296</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1404</v>
+        <v>1.8629</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7002</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>0.786</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4074</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1934</v>
+        <v>0.916</v>
       </c>
       <c r="V20" t="n">
         <v>1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1646</v>
+        <v>-3.6436</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.8952</v>
+        <v>-5.7835</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7306</v>
+        <v>2.1398</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3769</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8647</v>
+        <v>0.3857</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6008</v>
+        <v>-0.4891</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4656</v>
+        <v>0.8748</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2187</v>
+        <v>-4.5919</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.401</v>
+        <v>-4.954</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1823</v>
+        <v>0.3621</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6172</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.644</v>
+        <v>-0.0171</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9469</v>
+        <v>-0.4999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3029</v>
+        <v>0.4828</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.3219</v>
+        <v>-19.5767</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.3664</v>
+        <v>-22.3663</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0447</v>
+        <v>2.7896</v>
       </c>
       <c r="G23" t="n">
         <v>-15.9572</v>
@@ -2221,13 +2221,13 @@
         <v>-11.1521</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7278000000000002</v>
+        <v>-0.7277999999999993</v>
       </c>
       <c r="K23" t="n">
         <v>-3.7841</v>
       </c>
       <c r="L23" t="n">
-        <v>3.056100000000001</v>
+        <v>3.0561</v>
       </c>
       <c r="M23" t="n">
         <v>-15.2292</v>
@@ -2248,13 +2248,13 @@
         <v>16.313</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6851000000000002</v>
+        <v>0.06010000000000015</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.1662</v>
+        <v>-3.1664</v>
       </c>
       <c r="U23" t="n">
-        <v>2.4814</v>
+        <v>3.2265</v>
       </c>
       <c r="V23" t="n">
         <v>2.8457</v>
